--- a/20240411_system_analysis/output/20240411_system_analysis_element_pairs.xlsx
+++ b/20240411_system_analysis/output/20240411_system_analysis_element_pairs.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:C11"/>
+  <dimension ref="A1:C12"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -551,31 +551,46 @@
       </c>
     </row>
     <row r="9">
-      <c r="A9" t="inlineStr"/>
-      <c r="B9" t="inlineStr"/>
-      <c r="C9" t="inlineStr"/>
+      <c r="A9" t="inlineStr">
+        <is>
+          <t>1152569.cif</t>
+        </is>
+      </c>
+      <c r="B9" t="n">
+        <v>2.684</v>
+      </c>
+      <c r="C9" t="inlineStr">
+        <is>
+          <t>Full occupancy</t>
+        </is>
+      </c>
     </row>
     <row r="10">
-      <c r="A10" t="inlineStr">
-        <is>
-          <t>Average</t>
-        </is>
-      </c>
-      <c r="B10" t="n">
-        <v>2.611</v>
-      </c>
+      <c r="A10" t="inlineStr"/>
+      <c r="B10" t="inlineStr"/>
       <c r="C10" t="inlineStr"/>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
+          <t>Average</t>
+        </is>
+      </c>
+      <c r="B11" t="n">
+        <v>2.62</v>
+      </c>
+      <c r="C11" t="inlineStr"/>
+    </row>
+    <row r="12">
+      <c r="A12" t="inlineStr">
+        <is>
           <t>SD</t>
         </is>
       </c>
-      <c r="B11" t="n">
-        <v>0.032</v>
-      </c>
-      <c r="C11" t="inlineStr"/>
+      <c r="B12" t="n">
+        <v>0.039</v>
+      </c>
+      <c r="C12" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
